--- a/Flujo/Input/Reporte de Ventas/CONTROL DE VENTAS PRADA.xlsx
+++ b/Flujo/Input/Reporte de Ventas/CONTROL DE VENTAS PRADA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ehuamani\MAXX_Grupo_Inmobiliario\Flujo\Input\Reporte de Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C02203-2062-4025-BD49-2AEA16A8F2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D3A150-FF87-4172-ACD0-81677FFC6550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{83726F34-7180-44BA-8E01-7A2022CDB09D}"/>
   </bookViews>
@@ -3340,115 +3340,46 @@
     <xf numFmtId="164" fontId="50" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="52" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="63" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="63" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="80" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="52" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3462,6 +3393,75 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="97" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="80" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3876,31 +3876,31 @@
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.5">
-      <c r="B5" s="565"/>
-      <c r="C5" s="565"/>
-      <c r="D5" s="565"/>
+      <c r="B5" s="596"/>
+      <c r="C5" s="596"/>
+      <c r="D5" s="596"/>
     </row>
     <row r="7" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="D7" s="566" t="s">
+      <c r="D7" s="597" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="566"/>
-      <c r="F7" s="566"/>
-      <c r="G7" s="566"/>
-      <c r="H7" s="566"/>
-      <c r="I7" s="566"/>
-      <c r="J7" s="566"/>
-      <c r="K7" s="566"/>
-      <c r="L7" s="566"/>
-      <c r="M7" s="566"/>
-      <c r="N7" s="566"/>
-      <c r="O7" s="566"/>
-      <c r="P7" s="566"/>
-      <c r="Q7" s="566"/>
-      <c r="R7" s="566"/>
-      <c r="S7" s="566"/>
-      <c r="T7" s="566"/>
-      <c r="U7" s="566"/>
+      <c r="E7" s="597"/>
+      <c r="F7" s="597"/>
+      <c r="G7" s="597"/>
+      <c r="H7" s="597"/>
+      <c r="I7" s="597"/>
+      <c r="J7" s="597"/>
+      <c r="K7" s="597"/>
+      <c r="L7" s="597"/>
+      <c r="M7" s="597"/>
+      <c r="N7" s="597"/>
+      <c r="O7" s="597"/>
+      <c r="P7" s="597"/>
+      <c r="Q7" s="597"/>
+      <c r="R7" s="597"/>
+      <c r="S7" s="597"/>
+      <c r="T7" s="597"/>
+      <c r="U7" s="597"/>
     </row>
     <row r="11" spans="2:22" ht="49.2" x14ac:dyDescent="0.5">
       <c r="B11" s="7" t="s">
@@ -3998,7 +3998,7 @@
       <c r="N12" s="23">
         <v>3000</v>
       </c>
-      <c r="O12" s="563">
+      <c r="O12" s="561">
         <f>SUM(N12:N17)</f>
         <v>637000</v>
       </c>
@@ -4037,7 +4037,7 @@
       <c r="N13" s="23">
         <v>27000</v>
       </c>
-      <c r="O13" s="563"/>
+      <c r="O13" s="561"/>
       <c r="P13" s="14" t="s">
         <v>27</v>
       </c>
@@ -4071,7 +4071,7 @@
       <c r="N14" s="23">
         <v>3000</v>
       </c>
-      <c r="O14" s="563"/>
+      <c r="O14" s="561"/>
       <c r="P14" s="14" t="s">
         <v>27</v>
       </c>
@@ -4105,7 +4105,7 @@
       <c r="N15" s="23">
         <v>30000</v>
       </c>
-      <c r="O15" s="563"/>
+      <c r="O15" s="561"/>
       <c r="P15" s="14" t="s">
         <v>27</v>
       </c>
@@ -4139,7 +4139,7 @@
       <c r="N16" s="23">
         <v>700</v>
       </c>
-      <c r="O16" s="563"/>
+      <c r="O16" s="561"/>
       <c r="P16" s="14" t="s">
         <v>27</v>
       </c>
@@ -4173,7 +4173,7 @@
       <c r="N17" s="23">
         <v>573300</v>
       </c>
-      <c r="O17" s="563"/>
+      <c r="O17" s="561"/>
       <c r="P17" s="14" t="s">
         <v>30</v>
       </c>
@@ -4238,7 +4238,7 @@
       <c r="N19" s="53">
         <v>3000</v>
       </c>
-      <c r="O19" s="567">
+      <c r="O19" s="598">
         <f>SUM(N19:N24)</f>
         <v>679000</v>
       </c>
@@ -4278,7 +4278,7 @@
       <c r="N20" s="59">
         <v>150000</v>
       </c>
-      <c r="O20" s="568"/>
+      <c r="O20" s="599"/>
       <c r="P20" s="14" t="s">
         <v>27</v>
       </c>
@@ -4312,7 +4312,7 @@
       <c r="N21" s="59">
         <v>115000</v>
       </c>
-      <c r="O21" s="568"/>
+      <c r="O21" s="599"/>
       <c r="P21" s="14" t="s">
         <v>27</v>
       </c>
@@ -4346,7 +4346,7 @@
       <c r="N22" s="59">
         <v>21400</v>
       </c>
-      <c r="O22" s="568"/>
+      <c r="O22" s="599"/>
       <c r="P22" s="14" t="s">
         <v>27</v>
       </c>
@@ -4380,7 +4380,7 @@
       <c r="N23" s="59">
         <v>10600</v>
       </c>
-      <c r="O23" s="568"/>
+      <c r="O23" s="599"/>
       <c r="P23" s="14" t="s">
         <v>27</v>
       </c>
@@ -4414,7 +4414,7 @@
       <c r="N24" s="23">
         <v>379000</v>
       </c>
-      <c r="O24" s="568"/>
+      <c r="O24" s="599"/>
       <c r="P24" s="14" t="s">
         <v>30</v>
       </c>
@@ -4479,7 +4479,7 @@
       <c r="N26" s="75">
         <v>3000</v>
       </c>
-      <c r="O26" s="562">
+      <c r="O26" s="594">
         <f>SUM(N26:N28)</f>
         <v>520400</v>
       </c>
@@ -4519,7 +4519,7 @@
       <c r="N27" s="59">
         <v>117000</v>
       </c>
-      <c r="O27" s="563"/>
+      <c r="O27" s="561"/>
       <c r="P27" s="14" t="s">
         <v>41</v>
       </c>
@@ -4553,7 +4553,7 @@
       <c r="N28" s="23">
         <v>400400</v>
       </c>
-      <c r="O28" s="563"/>
+      <c r="O28" s="561"/>
       <c r="P28" s="14" t="s">
         <v>30</v>
       </c>
@@ -4629,7 +4629,7 @@
       <c r="N30" s="59">
         <v>3000</v>
       </c>
-      <c r="O30" s="564">
+      <c r="O30" s="595">
         <f>SUM(N30:N32)</f>
         <v>673700</v>
       </c>
@@ -4670,7 +4670,7 @@
       <c r="N31" s="59">
         <v>134740</v>
       </c>
-      <c r="O31" s="563"/>
+      <c r="O31" s="561"/>
       <c r="P31" s="14" t="s">
         <v>45</v>
       </c>
@@ -4706,7 +4706,7 @@
       <c r="N32" s="23">
         <v>535960</v>
       </c>
-      <c r="O32" s="563"/>
+      <c r="O32" s="561"/>
       <c r="P32" s="14" t="s">
         <v>30</v>
       </c>
@@ -4791,7 +4791,7 @@
       <c r="N35" s="114">
         <v>3000</v>
       </c>
-      <c r="O35" s="563">
+      <c r="O35" s="561">
         <f>SUM(N35:N40)</f>
         <v>622500</v>
       </c>
@@ -4825,7 +4825,7 @@
       <c r="N36" s="114">
         <v>20000</v>
       </c>
-      <c r="O36" s="563"/>
+      <c r="O36" s="561"/>
       <c r="P36" t="s">
         <v>27</v>
       </c>
@@ -4856,7 +4856,7 @@
       <c r="N37" s="114">
         <v>65000</v>
       </c>
-      <c r="O37" s="563"/>
+      <c r="O37" s="561"/>
       <c r="P37" t="s">
         <v>27</v>
       </c>
@@ -4887,7 +4887,7 @@
       <c r="N38" s="114">
         <v>22000</v>
       </c>
-      <c r="O38" s="563"/>
+      <c r="O38" s="561"/>
       <c r="P38" t="s">
         <v>27</v>
       </c>
@@ -4918,7 +4918,7 @@
       <c r="N39" s="41">
         <v>512500</v>
       </c>
-      <c r="O39" s="563"/>
+      <c r="O39" s="561"/>
       <c r="P39" t="s">
         <v>52</v>
       </c>
@@ -5003,7 +5003,7 @@
       <c r="N42" s="41">
         <v>3000</v>
       </c>
-      <c r="O42" s="563">
+      <c r="O42" s="561">
         <f>SUM(N42:N44)</f>
         <v>447080</v>
       </c>
@@ -5038,7 +5038,7 @@
       <c r="N43" s="41">
         <v>86560</v>
       </c>
-      <c r="O43" s="563"/>
+      <c r="O43" s="561"/>
       <c r="P43" t="s">
         <v>27</v>
       </c>
@@ -5070,7 +5070,7 @@
       <c r="N44" s="41">
         <v>357520</v>
       </c>
-      <c r="O44" s="563"/>
+      <c r="O44" s="561"/>
       <c r="P44" t="s">
         <v>52</v>
       </c>
@@ -5175,7 +5175,7 @@
       <c r="N48" s="41">
         <v>3000</v>
       </c>
-      <c r="O48" s="563">
+      <c r="O48" s="561">
         <f>SUM(N48:N61)</f>
         <v>710300</v>
       </c>
@@ -5210,7 +5210,7 @@
       <c r="N49" s="41">
         <v>281120</v>
       </c>
-      <c r="O49" s="563"/>
+      <c r="O49" s="561"/>
       <c r="P49" t="s">
         <v>27</v>
       </c>
@@ -5242,7 +5242,7 @@
       <c r="N50" s="41">
         <v>248605</v>
       </c>
-      <c r="O50" s="563"/>
+      <c r="O50" s="561"/>
       <c r="P50" t="s">
         <v>27</v>
       </c>
@@ -5274,7 +5274,7 @@
       <c r="N51" s="41">
         <v>20000</v>
       </c>
-      <c r="O51" s="563"/>
+      <c r="O51" s="561"/>
       <c r="P51" t="s">
         <v>27</v>
       </c>
@@ -5306,7 +5306,7 @@
       <c r="N52" s="41">
         <v>15515</v>
       </c>
-      <c r="O52" s="563"/>
+      <c r="O52" s="561"/>
       <c r="P52" t="s">
         <v>27</v>
       </c>
@@ -5338,7 +5338,7 @@
       <c r="N53" s="41">
         <v>20000</v>
       </c>
-      <c r="O53" s="563"/>
+      <c r="O53" s="561"/>
       <c r="P53"/>
       <c r="Q53" s="5" t="s">
         <v>254</v>
@@ -5365,7 +5365,7 @@
       <c r="N54" s="41">
         <v>15515</v>
       </c>
-      <c r="O54" s="563"/>
+      <c r="O54" s="561"/>
       <c r="P54"/>
       <c r="Q54" s="5" t="s">
         <v>255</v>
@@ -5392,7 +5392,7 @@
       <c r="N55" s="41">
         <v>20000</v>
       </c>
-      <c r="O55" s="563"/>
+      <c r="O55" s="561"/>
       <c r="P55"/>
       <c r="Q55" s="5" t="s">
         <v>256</v>
@@ -5419,7 +5419,7 @@
       <c r="N56" s="41">
         <v>15515</v>
       </c>
-      <c r="O56" s="563"/>
+      <c r="O56" s="561"/>
       <c r="P56"/>
       <c r="Q56" s="5" t="s">
         <v>257</v>
@@ -5446,7 +5446,7 @@
       <c r="N57" s="41">
         <v>20000</v>
       </c>
-      <c r="O57" s="563"/>
+      <c r="O57" s="561"/>
       <c r="P57"/>
       <c r="Q57" s="5" t="s">
         <v>258</v>
@@ -5473,7 +5473,7 @@
       <c r="N58" s="41">
         <v>15515</v>
       </c>
-      <c r="O58" s="563"/>
+      <c r="O58" s="561"/>
       <c r="P58"/>
       <c r="Q58" s="5" t="s">
         <v>259</v>
@@ -5500,7 +5500,7 @@
       <c r="N59" s="41">
         <v>20000</v>
       </c>
-      <c r="O59" s="563"/>
+      <c r="O59" s="561"/>
       <c r="P59"/>
       <c r="Q59" s="5" t="s">
         <v>260</v>
@@ -5527,7 +5527,7 @@
       <c r="N60" s="41">
         <v>15515</v>
       </c>
-      <c r="O60" s="563"/>
+      <c r="O60" s="561"/>
       <c r="P60"/>
       <c r="Q60" s="5" t="s">
         <v>261</v>
@@ -5693,7 +5693,7 @@
       <c r="N67" s="114">
         <v>2000</v>
       </c>
-      <c r="O67" s="560">
+      <c r="O67" s="583">
         <f>SUM(N67:N69)</f>
         <v>490000</v>
       </c>
@@ -5730,7 +5730,7 @@
       <c r="N68" s="114">
         <v>96000</v>
       </c>
-      <c r="O68" s="560"/>
+      <c r="O68" s="583"/>
       <c r="P68"/>
       <c r="Q68" s="5" t="s">
         <v>262</v>
@@ -5757,7 +5757,7 @@
       <c r="N69" s="41">
         <v>392000</v>
       </c>
-      <c r="O69" s="580"/>
+      <c r="O69" s="600"/>
       <c r="P69" t="s">
         <v>45</v>
       </c>
@@ -5819,7 +5819,7 @@
       <c r="N71" s="114">
         <v>3000</v>
       </c>
-      <c r="O71" s="559">
+      <c r="O71" s="592">
         <f>SUM(N71:N75)</f>
         <v>630000</v>
       </c>
@@ -5856,7 +5856,7 @@
       <c r="N72" s="114">
         <v>55000</v>
       </c>
-      <c r="O72" s="560"/>
+      <c r="O72" s="583"/>
       <c r="P72" t="s">
         <v>45</v>
       </c>
@@ -5887,7 +5887,7 @@
       <c r="N73" s="114">
         <v>44000</v>
       </c>
-      <c r="O73" s="560"/>
+      <c r="O73" s="583"/>
       <c r="P73" s="545"/>
       <c r="Q73" s="5" t="s">
         <v>265</v>
@@ -5913,7 +5913,7 @@
       <c r="N74" s="114">
         <v>68000</v>
       </c>
-      <c r="O74" s="560"/>
+      <c r="O74" s="583"/>
       <c r="P74" s="545"/>
       <c r="Q74" s="5" t="s">
         <v>266</v>
@@ -5939,7 +5939,7 @@
       <c r="N75" s="176">
         <v>460000</v>
       </c>
-      <c r="O75" s="561"/>
+      <c r="O75" s="593"/>
       <c r="P75" s="546"/>
       <c r="Q75" s="5" t="s">
         <v>267</v>
@@ -6002,7 +6002,7 @@
       <c r="N77" s="114">
         <v>3000</v>
       </c>
-      <c r="O77" s="569">
+      <c r="O77" s="585">
         <f>SUM(N77:N83)</f>
         <v>435500</v>
       </c>
@@ -6039,7 +6039,7 @@
       <c r="N78" s="114">
         <v>20000</v>
       </c>
-      <c r="O78" s="569"/>
+      <c r="O78" s="585"/>
       <c r="P78" t="s">
         <v>45</v>
       </c>
@@ -6070,7 +6070,7 @@
       <c r="N79" s="114">
         <v>10000</v>
       </c>
-      <c r="O79" s="569"/>
+      <c r="O79" s="585"/>
       <c r="P79" t="s">
         <v>45</v>
       </c>
@@ -6101,7 +6101,7 @@
       <c r="N80" s="114">
         <v>10000</v>
       </c>
-      <c r="O80" s="569"/>
+      <c r="O80" s="585"/>
       <c r="P80" t="s">
         <v>45</v>
       </c>
@@ -6132,7 +6132,7 @@
       <c r="N81" s="114">
         <v>550</v>
       </c>
-      <c r="O81" s="569"/>
+      <c r="O81" s="585"/>
       <c r="P81" t="s">
         <v>45</v>
       </c>
@@ -6163,7 +6163,7 @@
       <c r="N82" s="41">
         <v>21000</v>
       </c>
-      <c r="O82" s="569"/>
+      <c r="O82" s="585"/>
       <c r="P82" s="547"/>
       <c r="Q82" s="5" t="s">
         <v>272</v>
@@ -6190,7 +6190,7 @@
       <c r="N83" s="197">
         <v>370950</v>
       </c>
-      <c r="O83" s="570"/>
+      <c r="O83" s="586"/>
       <c r="P83" s="548"/>
       <c r="Q83" s="198" t="s">
         <v>273</v>
@@ -6479,7 +6479,7 @@
       <c r="N96" s="114">
         <v>3000</v>
       </c>
-      <c r="O96" s="574">
+      <c r="O96" s="570">
         <f>SUM(N96:N101)</f>
         <v>495000</v>
       </c>
@@ -6516,7 +6516,7 @@
       <c r="N97" s="114">
         <v>187000</v>
       </c>
-      <c r="O97" s="574"/>
+      <c r="O97" s="570"/>
       <c r="P97" s="226" t="s">
         <v>149</v>
       </c>
@@ -6545,7 +6545,7 @@
       <c r="N98" s="41">
         <v>120000</v>
       </c>
-      <c r="O98" s="574"/>
+      <c r="O98" s="570"/>
       <c r="P98" s="226" t="s">
         <v>152</v>
       </c>
@@ -6574,7 +6574,7 @@
       <c r="N99" s="41">
         <v>155000</v>
       </c>
-      <c r="O99" s="574"/>
+      <c r="O99" s="570"/>
       <c r="P99" s="227" t="s">
         <v>154</v>
       </c>
@@ -6603,7 +6603,7 @@
       <c r="N100" s="41">
         <v>18000</v>
       </c>
-      <c r="O100" s="574"/>
+      <c r="O100" s="570"/>
       <c r="P100" s="227" t="s">
         <v>276</v>
       </c>
@@ -6632,7 +6632,7 @@
       <c r="N101" s="114">
         <v>12000</v>
       </c>
-      <c r="O101" s="574"/>
+      <c r="O101" s="570"/>
       <c r="P101" s="227" t="s">
         <v>155</v>
       </c>
@@ -6820,7 +6820,7 @@
       <c r="N109" s="114">
         <v>3000</v>
       </c>
-      <c r="O109" s="563">
+      <c r="O109" s="561">
         <f>SUM(N109:N112)</f>
         <v>654000</v>
       </c>
@@ -6857,7 +6857,7 @@
       <c r="N110" s="114">
         <v>97800</v>
       </c>
-      <c r="O110" s="563"/>
+      <c r="O110" s="561"/>
       <c r="P110" t="s">
         <v>27</v>
       </c>
@@ -6888,7 +6888,7 @@
       <c r="N111" s="114">
         <v>30000</v>
       </c>
-      <c r="O111" s="563"/>
+      <c r="O111" s="561"/>
       <c r="P111" t="s">
         <v>27</v>
       </c>
@@ -6920,7 +6920,7 @@
       <c r="N112" s="141">
         <v>523200</v>
       </c>
-      <c r="O112" s="571"/>
+      <c r="O112" s="562"/>
       <c r="P112" s="143" t="s">
         <v>61</v>
       </c>
@@ -7137,7 +7137,7 @@
       <c r="N121" s="114">
         <v>3000</v>
       </c>
-      <c r="O121" s="572">
+      <c r="O121" s="560">
         <f>SUM(N121:N124)</f>
         <v>612000</v>
       </c>
@@ -7171,7 +7171,7 @@
       <c r="N122" s="114">
         <v>29500</v>
       </c>
-      <c r="O122" s="572"/>
+      <c r="O122" s="560"/>
       <c r="P122" t="s">
         <v>27</v>
       </c>
@@ -7202,7 +7202,7 @@
       <c r="N123" s="114">
         <v>29500</v>
       </c>
-      <c r="O123" s="572"/>
+      <c r="O123" s="560"/>
       <c r="P123"/>
       <c r="Q123" s="5" t="s">
         <v>290</v>
@@ -7227,7 +7227,7 @@
       <c r="N124" s="272">
         <v>550000</v>
       </c>
-      <c r="O124" s="573"/>
+      <c r="O124" s="587"/>
       <c r="P124" s="549"/>
       <c r="Q124" s="5" t="s">
         <v>289</v>
@@ -7388,7 +7388,7 @@
       <c r="N131" s="41">
         <v>3000</v>
       </c>
-      <c r="O131" s="575">
+      <c r="O131" s="578">
         <f>SUM(N131:N133)</f>
         <v>165000</v>
       </c>
@@ -7419,7 +7419,7 @@
       <c r="N132" s="41">
         <v>162</v>
       </c>
-      <c r="O132" s="576"/>
+      <c r="O132" s="588"/>
       <c r="P132" s="274" t="s">
         <v>27</v>
       </c>
@@ -7447,7 +7447,7 @@
       <c r="N133" s="41">
         <v>161838</v>
       </c>
-      <c r="O133" s="576"/>
+      <c r="O133" s="588"/>
       <c r="P133" s="274" t="s">
         <v>64</v>
       </c>
@@ -7709,7 +7709,7 @@
       <c r="N144" s="200">
         <v>3000</v>
       </c>
-      <c r="O144" s="577">
+      <c r="O144" s="589">
         <f>+N144+N145</f>
         <v>13000</v>
       </c>
@@ -7737,7 +7737,7 @@
       <c r="N145" s="200">
         <v>10000</v>
       </c>
-      <c r="O145" s="575"/>
+      <c r="O145" s="578"/>
       <c r="Q145" s="5" t="s">
         <v>302</v>
       </c>
@@ -7823,7 +7823,7 @@
       <c r="N149" s="114">
         <v>3000</v>
       </c>
-      <c r="O149" s="578">
+      <c r="O149" s="590">
         <f>SUM(N149:N154)</f>
         <v>475000</v>
       </c>
@@ -7860,7 +7860,7 @@
       <c r="N150" s="114">
         <v>20000</v>
       </c>
-      <c r="O150" s="578"/>
+      <c r="O150" s="590"/>
       <c r="P150" t="s">
         <v>45</v>
       </c>
@@ -7891,7 +7891,7 @@
       <c r="N151" s="114">
         <v>10000</v>
       </c>
-      <c r="O151" s="578"/>
+      <c r="O151" s="590"/>
       <c r="P151" t="s">
         <v>45</v>
       </c>
@@ -7922,7 +7922,7 @@
       <c r="N152" s="296">
         <v>30000</v>
       </c>
-      <c r="O152" s="578"/>
+      <c r="O152" s="590"/>
       <c r="P152" t="s">
         <v>45</v>
       </c>
@@ -7953,7 +7953,7 @@
       <c r="N153" s="41">
         <v>427000</v>
       </c>
-      <c r="O153" s="578"/>
+      <c r="O153" s="590"/>
       <c r="P153"/>
       <c r="Q153" s="5" t="s">
         <v>70</v>
@@ -7980,7 +7980,7 @@
       <c r="N154" s="298">
         <v>-15000</v>
       </c>
-      <c r="O154" s="579"/>
+      <c r="O154" s="591"/>
       <c r="P154" s="161" t="s">
         <v>52</v>
       </c>
@@ -8051,7 +8051,7 @@
       <c r="N156" s="114">
         <v>3000</v>
       </c>
-      <c r="O156" s="563">
+      <c r="O156" s="561">
         <f>+N156+N157+N158</f>
         <v>690000</v>
       </c>
@@ -8081,7 +8081,7 @@
       <c r="N157" s="114">
         <v>107000</v>
       </c>
-      <c r="O157" s="563"/>
+      <c r="O157" s="561"/>
       <c r="P157" s="545"/>
       <c r="Q157" s="5" t="s">
         <v>74</v>
@@ -8106,7 +8106,7 @@
       <c r="N158" s="41">
         <v>580000</v>
       </c>
-      <c r="O158" s="563"/>
+      <c r="O158" s="561"/>
       <c r="P158" s="545"/>
       <c r="Q158" s="5" t="s">
         <v>75</v>
@@ -8267,11 +8267,11 @@
       <c r="N165" s="114">
         <v>3000</v>
       </c>
-      <c r="O165" s="563">
+      <c r="O165" s="561">
         <f>SUM(N165:N168)</f>
         <v>654000</v>
       </c>
-      <c r="P165" s="560" t="s">
+      <c r="P165" s="583" t="s">
         <v>24</v>
       </c>
       <c r="Q165" s="5" t="s">
@@ -8305,8 +8305,8 @@
       <c r="N166" s="114">
         <v>25000</v>
       </c>
-      <c r="O166" s="563"/>
-      <c r="P166" s="560"/>
+      <c r="O166" s="561"/>
+      <c r="P166" s="583"/>
       <c r="Q166" s="5" t="s">
         <v>304</v>
       </c>
@@ -8334,8 +8334,8 @@
       <c r="N167" s="41">
         <v>37400</v>
       </c>
-      <c r="O167" s="563"/>
-      <c r="P167" s="560"/>
+      <c r="O167" s="561"/>
+      <c r="P167" s="583"/>
       <c r="Q167" s="5" t="s">
         <v>305</v>
       </c>
@@ -8360,8 +8360,8 @@
       <c r="N168" s="41">
         <v>588600</v>
       </c>
-      <c r="O168" s="563"/>
-      <c r="P168" s="560"/>
+      <c r="O168" s="561"/>
+      <c r="P168" s="583"/>
       <c r="Q168" s="5" t="s">
         <v>306</v>
       </c>
@@ -8512,7 +8512,7 @@
       <c r="N173" s="114">
         <v>3000</v>
       </c>
-      <c r="O173" s="563">
+      <c r="O173" s="561">
         <f>SUM(N173:N175)</f>
         <v>558300</v>
       </c>
@@ -8549,7 +8549,7 @@
       <c r="N174" s="114">
         <v>52830</v>
       </c>
-      <c r="O174" s="563"/>
+      <c r="O174" s="561"/>
       <c r="P174" t="s">
         <v>27</v>
       </c>
@@ -8582,7 +8582,7 @@
       <c r="N175" s="141">
         <v>502470</v>
       </c>
-      <c r="O175" s="571"/>
+      <c r="O175" s="562"/>
       <c r="P175" s="143" t="s">
         <v>30</v>
       </c>
@@ -8630,7 +8630,7 @@
       <c r="N176" s="114">
         <v>3000</v>
       </c>
-      <c r="O176" s="563">
+      <c r="O176" s="561">
         <f>SUM(N176:N179)</f>
         <v>592500</v>
       </c>
@@ -8664,7 +8664,7 @@
       <c r="N177" s="114">
         <v>48000</v>
       </c>
-      <c r="O177" s="563"/>
+      <c r="O177" s="561"/>
       <c r="P177" t="s">
         <v>27</v>
       </c>
@@ -8695,7 +8695,7 @@
       <c r="N178" s="114">
         <v>8250</v>
       </c>
-      <c r="O178" s="563"/>
+      <c r="O178" s="561"/>
       <c r="P178" t="s">
         <v>27</v>
       </c>
@@ -8727,7 +8727,7 @@
       <c r="N179" s="331">
         <v>533250</v>
       </c>
-      <c r="O179" s="581"/>
+      <c r="O179" s="584"/>
       <c r="P179" s="161" t="s">
         <v>84</v>
       </c>
@@ -8888,7 +8888,7 @@
       <c r="N185" s="336">
         <v>3000</v>
       </c>
-      <c r="O185" s="587">
+      <c r="O185" s="582">
         <f>SUM(N185:N198)</f>
         <v>711500</v>
       </c>
@@ -8922,7 +8922,7 @@
       <c r="N186" s="114">
         <v>291500</v>
       </c>
-      <c r="O186" s="587"/>
+      <c r="O186" s="582"/>
       <c r="P186" s="550"/>
       <c r="Q186" s="5" t="s">
         <v>87</v>
@@ -8948,7 +8948,7 @@
       <c r="N187" s="114">
         <v>34750</v>
       </c>
-      <c r="O187" s="587"/>
+      <c r="O187" s="582"/>
       <c r="P187" s="550"/>
       <c r="Q187" s="5" t="s">
         <v>88</v>
@@ -8974,7 +8974,7 @@
       <c r="N188" s="114">
         <v>34750</v>
       </c>
-      <c r="O188" s="587"/>
+      <c r="O188" s="582"/>
       <c r="P188" s="550"/>
       <c r="Q188" s="5" t="s">
         <v>89</v>
@@ -9000,7 +9000,7 @@
       <c r="N189" s="114">
         <v>34750</v>
       </c>
-      <c r="O189" s="587"/>
+      <c r="O189" s="582"/>
       <c r="P189" s="550"/>
       <c r="Q189" s="5" t="s">
         <v>90</v>
@@ -9026,7 +9026,7 @@
       <c r="N190" s="41">
         <v>34750</v>
       </c>
-      <c r="O190" s="587"/>
+      <c r="O190" s="582"/>
       <c r="P190" s="550"/>
       <c r="Q190" s="5" t="s">
         <v>91</v>
@@ -9052,7 +9052,7 @@
       <c r="N191" s="41">
         <v>34750</v>
       </c>
-      <c r="O191" s="587"/>
+      <c r="O191" s="582"/>
       <c r="P191" s="550"/>
       <c r="Q191" s="5" t="s">
         <v>92</v>
@@ -9078,7 +9078,7 @@
       <c r="N192" s="41">
         <v>34750</v>
       </c>
-      <c r="O192" s="587"/>
+      <c r="O192" s="582"/>
       <c r="P192" s="550"/>
       <c r="Q192" s="5" t="s">
         <v>93</v>
@@ -9104,7 +9104,7 @@
       <c r="N193" s="41">
         <v>34750</v>
       </c>
-      <c r="O193" s="587"/>
+      <c r="O193" s="582"/>
       <c r="P193" s="550"/>
       <c r="Q193" s="5" t="s">
         <v>94</v>
@@ -9130,7 +9130,7 @@
       <c r="N194" s="41">
         <v>34750</v>
       </c>
-      <c r="O194" s="587"/>
+      <c r="O194" s="582"/>
       <c r="P194" s="550"/>
       <c r="Q194" s="5" t="s">
         <v>95</v>
@@ -9156,7 +9156,7 @@
       <c r="N195" s="41">
         <v>34750</v>
       </c>
-      <c r="O195" s="587"/>
+      <c r="O195" s="582"/>
       <c r="P195" s="550"/>
       <c r="Q195" s="5" t="s">
         <v>96</v>
@@ -9180,7 +9180,7 @@
       <c r="N196" s="41">
         <v>34750</v>
       </c>
-      <c r="O196" s="587"/>
+      <c r="O196" s="582"/>
       <c r="P196" s="550"/>
       <c r="Q196" s="5" t="s">
         <v>97</v>
@@ -9204,7 +9204,7 @@
       <c r="N197" s="41">
         <v>34750</v>
       </c>
-      <c r="O197" s="587"/>
+      <c r="O197" s="582"/>
       <c r="P197" s="550"/>
       <c r="Q197" s="5" t="s">
         <v>98</v>
@@ -9228,7 +9228,7 @@
       <c r="N198" s="41">
         <v>34750</v>
       </c>
-      <c r="O198" s="587"/>
+      <c r="O198" s="582"/>
       <c r="P198" s="550"/>
       <c r="Q198" s="5" t="s">
         <v>309</v>
@@ -9287,7 +9287,7 @@
       <c r="N200" s="318">
         <v>3000</v>
       </c>
-      <c r="O200" s="590">
+      <c r="O200" s="563">
         <f>+N200+N201+N202</f>
         <v>417700</v>
       </c>
@@ -9320,7 +9320,7 @@
       <c r="N201" s="41">
         <v>47000</v>
       </c>
-      <c r="O201" s="563"/>
+      <c r="O201" s="561"/>
       <c r="P201" s="552"/>
       <c r="Q201" s="5" t="s">
         <v>101</v>
@@ -9347,7 +9347,7 @@
       <c r="N202" s="172">
         <v>367700</v>
       </c>
-      <c r="O202" s="591"/>
+      <c r="O202" s="564"/>
       <c r="P202" s="553"/>
       <c r="Q202" s="234" t="s">
         <v>102</v>
@@ -9404,7 +9404,7 @@
       <c r="N204" s="114">
         <v>200</v>
       </c>
-      <c r="O204" s="563">
+      <c r="O204" s="561">
         <f>SUM(N204:N209)</f>
         <v>496000</v>
       </c>
@@ -9436,7 +9436,7 @@
       <c r="N205" s="114">
         <v>2800</v>
       </c>
-      <c r="O205" s="563"/>
+      <c r="O205" s="561"/>
       <c r="P205" s="554"/>
       <c r="Q205" s="5" t="s">
         <v>104</v>
@@ -9462,7 +9462,7 @@
       <c r="N206" s="114">
         <v>25000</v>
       </c>
-      <c r="O206" s="563"/>
+      <c r="O206" s="561"/>
       <c r="P206" s="554"/>
       <c r="Q206" s="5" t="s">
         <v>104</v>
@@ -9488,7 +9488,7 @@
       <c r="N207" s="114">
         <v>7000</v>
       </c>
-      <c r="O207" s="563"/>
+      <c r="O207" s="561"/>
       <c r="P207" s="554"/>
       <c r="Q207" s="5" t="s">
         <v>105</v>
@@ -9514,7 +9514,7 @@
       <c r="N208" s="41">
         <v>24800</v>
       </c>
-      <c r="O208" s="563"/>
+      <c r="O208" s="561"/>
       <c r="P208" s="554"/>
       <c r="Q208" s="5" t="s">
         <v>106</v>
@@ -9540,7 +9540,7 @@
       <c r="N209" s="41">
         <v>436200</v>
       </c>
-      <c r="O209" s="563"/>
+      <c r="O209" s="561"/>
       <c r="P209" s="554"/>
       <c r="Q209" s="5" t="s">
         <v>107</v>
@@ -9645,7 +9645,7 @@
       <c r="N213" s="41">
         <v>3000</v>
       </c>
-      <c r="O213" s="572">
+      <c r="O213" s="560">
         <f>SUM(N213:N217)</f>
         <v>630000</v>
       </c>
@@ -9673,7 +9673,7 @@
       <c r="N214" s="41">
         <v>50000</v>
       </c>
-      <c r="O214" s="572"/>
+      <c r="O214" s="560"/>
       <c r="P214" s="555"/>
       <c r="Q214" s="5" t="s">
         <v>111</v>
@@ -9698,7 +9698,7 @@
       <c r="N215" s="41">
         <v>50000</v>
       </c>
-      <c r="O215" s="572"/>
+      <c r="O215" s="560"/>
       <c r="P215" s="555"/>
       <c r="Q215" s="5" t="s">
         <v>112</v>
@@ -9720,7 +9720,7 @@
       <c r="N216" s="114">
         <v>23000</v>
       </c>
-      <c r="O216" s="572"/>
+      <c r="O216" s="560"/>
       <c r="P216" s="555"/>
       <c r="Q216" s="5" t="s">
         <v>310</v>
@@ -9742,7 +9742,7 @@
       <c r="N217" s="114">
         <v>504000</v>
       </c>
-      <c r="O217" s="572"/>
+      <c r="O217" s="560"/>
       <c r="P217" s="555"/>
       <c r="Q217" s="5" t="s">
         <v>311</v>
@@ -9793,7 +9793,7 @@
       <c r="N219" s="354">
         <v>3000</v>
       </c>
-      <c r="O219" s="588">
+      <c r="O219" s="572">
         <f>SUM(N219:N222)</f>
         <v>407914</v>
       </c>
@@ -9822,7 +9822,7 @@
       <c r="N220" s="336">
         <v>9400</v>
       </c>
-      <c r="O220" s="572"/>
+      <c r="O220" s="560"/>
       <c r="P220" s="202"/>
     </row>
     <row r="221" spans="2:22" ht="24" customHeight="1" x14ac:dyDescent="0.5">
@@ -9842,7 +9842,7 @@
       <c r="N221" s="114">
         <v>23514</v>
       </c>
-      <c r="O221" s="572"/>
+      <c r="O221" s="560"/>
       <c r="P221" s="520"/>
       <c r="Q221" s="5" t="s">
         <v>312</v>
@@ -9865,7 +9865,7 @@
       <c r="N222" s="114">
         <v>372000</v>
       </c>
-      <c r="O222" s="572"/>
+      <c r="O222" s="560"/>
       <c r="Q222" s="5" t="s">
         <v>313</v>
       </c>
@@ -9932,7 +9932,7 @@
       <c r="K225" s="244">
         <v>55800</v>
       </c>
-      <c r="L225" s="592">
+      <c r="L225" s="567">
         <f>+H225+K225+K226</f>
         <v>769800</v>
       </c>
@@ -9942,7 +9942,7 @@
       <c r="N225" s="41">
         <v>3000</v>
       </c>
-      <c r="O225" s="594">
+      <c r="O225" s="569">
         <f>SUM(N225:N236)</f>
         <v>749372.92353999999</v>
       </c>
@@ -9972,7 +9972,7 @@
       <c r="K226" s="244">
         <v>60000</v>
       </c>
-      <c r="L226" s="593"/>
+      <c r="L226" s="568"/>
       <c r="M226" s="40">
         <v>45853</v>
       </c>
@@ -9980,7 +9980,7 @@
         <f>15651.69*3.555</f>
         <v>55641.757950000007</v>
       </c>
-      <c r="O226" s="574"/>
+      <c r="O226" s="570"/>
       <c r="Q226" s="5" t="s">
         <v>116</v>
       </c>
@@ -10006,7 +10006,7 @@
         <f>70000*3.555</f>
         <v>248850</v>
       </c>
-      <c r="O227" s="574"/>
+      <c r="O227" s="570"/>
       <c r="Q227" s="5" t="s">
         <v>117</v>
       </c>
@@ -10032,7 +10032,7 @@
         <f>7500*3.527</f>
         <v>26452.5</v>
       </c>
-      <c r="O228" s="574"/>
+      <c r="O228" s="570"/>
       <c r="Q228" s="5" t="s">
         <v>118</v>
       </c>
@@ -10058,7 +10058,7 @@
         <f>7500*3.522</f>
         <v>26415</v>
       </c>
-      <c r="O229" s="574"/>
+      <c r="O229" s="570"/>
       <c r="Q229" s="5" t="s">
         <v>119</v>
       </c>
@@ -10084,7 +10084,7 @@
         <f>3534.51*3.509</f>
         <v>12402.595590000001</v>
       </c>
-      <c r="O230" s="574"/>
+      <c r="O230" s="570"/>
       <c r="Q230" s="5" t="s">
         <v>120</v>
       </c>
@@ -10110,7 +10110,7 @@
         <f>7500*3.452</f>
         <v>25890</v>
       </c>
-      <c r="O231" s="574"/>
+      <c r="O231" s="570"/>
       <c r="Q231" s="5" t="s">
         <v>121</v>
       </c>
@@ -10136,7 +10136,7 @@
         <f>7500*3.443</f>
         <v>25822.5</v>
       </c>
-      <c r="O232" s="574"/>
+      <c r="O232" s="570"/>
       <c r="Q232" s="5" t="s">
         <v>122</v>
       </c>
@@ -10161,7 +10161,7 @@
       <c r="N233" s="41">
         <v>12165.78</v>
       </c>
-      <c r="O233" s="574"/>
+      <c r="O233" s="570"/>
       <c r="Q233" s="5" t="s">
         <v>123</v>
       </c>
@@ -10186,7 +10186,7 @@
       <c r="N234" s="41">
         <v>187884.33</v>
       </c>
-      <c r="O234" s="574"/>
+      <c r="O234" s="570"/>
       <c r="Q234" s="5" t="s">
         <v>124</v>
       </c>
@@ -10211,7 +10211,7 @@
       <c r="N235" s="41">
         <v>124848.46</v>
       </c>
-      <c r="O235" s="574"/>
+      <c r="O235" s="570"/>
       <c r="Q235" s="5" t="s">
         <v>337</v>
       </c>
@@ -10490,7 +10490,9 @@
         <f>SUM(H247:K247)</f>
         <v>743500</v>
       </c>
-      <c r="M247" s="40"/>
+      <c r="M247" s="40">
+        <v>46082</v>
+      </c>
       <c r="N247" s="114">
         <v>3000</v>
       </c>
@@ -10607,11 +10609,11 @@
       <c r="N253" s="41">
         <v>3000</v>
       </c>
-      <c r="O253" s="586">
+      <c r="O253" s="581">
         <f>SUM(N253:N255)</f>
         <v>484000</v>
       </c>
-      <c r="P253" s="585" t="s">
+      <c r="P253" s="580" t="s">
         <v>24</v>
       </c>
       <c r="Q253" s="5" t="s">
@@ -10634,8 +10636,8 @@
       <c r="N254" s="501">
         <v>45400</v>
       </c>
-      <c r="O254" s="586"/>
-      <c r="P254" s="585"/>
+      <c r="O254" s="581"/>
+      <c r="P254" s="580"/>
       <c r="Q254" s="5" t="s">
         <v>329</v>
       </c>
@@ -10656,8 +10658,8 @@
       <c r="N255" s="501">
         <v>435600</v>
       </c>
-      <c r="O255" s="586"/>
-      <c r="P255" s="585"/>
+      <c r="O255" s="581"/>
+      <c r="P255" s="580"/>
       <c r="Q255" s="5" t="s">
         <v>328</v>
       </c>
@@ -10727,7 +10729,7 @@
       <c r="N258" s="370">
         <v>3000</v>
       </c>
-      <c r="O258" s="582">
+      <c r="O258" s="579">
         <f>SUM(N258:N272)</f>
         <v>692000</v>
       </c>
@@ -10762,7 +10764,7 @@
       <c r="N259" s="370">
         <v>56300</v>
       </c>
-      <c r="O259" s="582"/>
+      <c r="O259" s="579"/>
       <c r="P259" s="556"/>
       <c r="Q259" s="371" t="s">
         <v>129</v>
@@ -10790,7 +10792,7 @@
       <c r="N260" s="370">
         <v>-56300</v>
       </c>
-      <c r="O260" s="582"/>
+      <c r="O260" s="579"/>
       <c r="P260" s="556"/>
       <c r="Q260" s="371" t="s">
         <v>130</v>
@@ -10818,7 +10820,7 @@
       <c r="N261" s="370">
         <v>82100</v>
       </c>
-      <c r="O261" s="582"/>
+      <c r="O261" s="579"/>
       <c r="P261" s="556"/>
       <c r="Q261" s="371" t="s">
         <v>131</v>
@@ -10845,7 +10847,7 @@
       <c r="N262" s="370">
         <v>9000</v>
       </c>
-      <c r="O262" s="582"/>
+      <c r="O262" s="579"/>
       <c r="P262" s="556"/>
       <c r="Q262" s="371" t="s">
         <v>132</v>
@@ -10872,7 +10874,7 @@
       <c r="N263" s="370">
         <v>553900</v>
       </c>
-      <c r="O263" s="582"/>
+      <c r="O263" s="579"/>
       <c r="P263" s="556"/>
       <c r="Q263" s="371" t="s">
         <v>133</v>
@@ -10895,7 +10897,7 @@
       <c r="N264" s="370">
         <v>-300</v>
       </c>
-      <c r="O264" s="582"/>
+      <c r="O264" s="579"/>
       <c r="P264" s="556"/>
       <c r="Q264" s="371" t="s">
         <v>134</v>
@@ -10922,7 +10924,7 @@
       <c r="N265" s="370">
         <v>9000</v>
       </c>
-      <c r="O265" s="582"/>
+      <c r="O265" s="579"/>
       <c r="P265" s="556"/>
       <c r="Q265" s="371" t="s">
         <v>135</v>
@@ -10949,7 +10951,7 @@
       <c r="N266" s="370">
         <v>9500</v>
       </c>
-      <c r="O266" s="582"/>
+      <c r="O266" s="579"/>
       <c r="P266" s="556"/>
       <c r="Q266" s="371" t="s">
         <v>136</v>
@@ -10979,7 +10981,7 @@
       <c r="N267" s="370">
         <v>2500</v>
       </c>
-      <c r="O267" s="582"/>
+      <c r="O267" s="579"/>
       <c r="P267" s="556"/>
       <c r="Q267" s="371" t="s">
         <v>138</v>
@@ -11006,7 +11008,7 @@
       <c r="N268" s="370">
         <v>6500</v>
       </c>
-      <c r="O268" s="582"/>
+      <c r="O268" s="579"/>
       <c r="P268" s="556"/>
       <c r="Q268" s="371" t="s">
         <v>139</v>
@@ -11032,7 +11034,7 @@
       <c r="N269" s="370">
         <v>9000</v>
       </c>
-      <c r="O269" s="582"/>
+      <c r="O269" s="579"/>
       <c r="P269" s="556"/>
       <c r="Q269" s="371" t="s">
         <v>140</v>
@@ -11058,7 +11060,7 @@
       <c r="N270" s="370">
         <v>-9500</v>
       </c>
-      <c r="O270" s="582"/>
+      <c r="O270" s="579"/>
       <c r="P270" s="556"/>
       <c r="Q270" s="5" t="s">
         <v>141</v>
@@ -11084,7 +11086,7 @@
       <c r="N271" s="370">
         <v>9000</v>
       </c>
-      <c r="O271" s="582"/>
+      <c r="O271" s="579"/>
       <c r="P271" s="556"/>
       <c r="Q271" s="5" t="s">
         <v>142</v>
@@ -11108,7 +11110,7 @@
       <c r="N272" s="370">
         <v>8300</v>
       </c>
-      <c r="O272" s="582"/>
+      <c r="O272" s="579"/>
       <c r="P272" s="556"/>
       <c r="Q272" s="5" t="s">
         <v>143</v>
@@ -11305,7 +11307,7 @@
       <c r="N280" s="501">
         <v>3000</v>
       </c>
-      <c r="O280" s="583">
+      <c r="O280" s="565">
         <f>SUM(N280:N282)</f>
         <v>535000</v>
       </c>
@@ -11330,7 +11332,7 @@
       <c r="N281" s="501">
         <v>50500</v>
       </c>
-      <c r="O281" s="584"/>
+      <c r="O281" s="566"/>
       <c r="P281" s="557"/>
       <c r="Q281" s="5" t="s">
         <v>319</v>
@@ -11352,7 +11354,7 @@
       <c r="N282" s="501">
         <v>481500</v>
       </c>
-      <c r="O282" s="584"/>
+      <c r="O282" s="566"/>
       <c r="P282" s="557"/>
       <c r="Q282" s="5" t="s">
         <v>320</v>
@@ -11412,7 +11414,7 @@
       <c r="N284" s="41">
         <v>3019</v>
       </c>
-      <c r="O284" s="589">
+      <c r="O284" s="559">
         <f>+N285+N284</f>
         <v>13019</v>
       </c>
@@ -11440,7 +11442,7 @@
       <c r="N285" s="41">
         <v>10000</v>
       </c>
-      <c r="O285" s="572"/>
+      <c r="O285" s="560"/>
       <c r="P285" s="202"/>
       <c r="Q285" s="5" t="s">
         <v>146</v>
@@ -12179,7 +12181,7 @@
       <c r="N317" s="383">
         <v>3000</v>
       </c>
-      <c r="O317" s="563">
+      <c r="O317" s="561">
         <f>SUM(N317:N322)</f>
         <v>397000</v>
       </c>
@@ -12211,7 +12213,7 @@
       <c r="N318" s="383">
         <v>23450</v>
       </c>
-      <c r="O318" s="563"/>
+      <c r="O318" s="561"/>
       <c r="P318" s="545"/>
       <c r="Q318" s="5" t="s">
         <v>157</v>
@@ -12238,7 +12240,7 @@
       <c r="N319" s="383">
         <v>78000</v>
       </c>
-      <c r="O319" s="563"/>
+      <c r="O319" s="561"/>
       <c r="P319" s="545"/>
       <c r="Q319" s="5" t="s">
         <v>159</v>
@@ -12265,7 +12267,7 @@
       <c r="N320" s="383">
         <v>34454.57</v>
       </c>
-      <c r="O320" s="563"/>
+      <c r="O320" s="561"/>
       <c r="P320" s="545"/>
       <c r="Q320" s="5" t="s">
         <v>160</v>
@@ -12292,7 +12294,7 @@
       <c r="N321" s="383">
         <v>45.43</v>
       </c>
-      <c r="O321" s="563"/>
+      <c r="O321" s="561"/>
       <c r="P321" s="545"/>
       <c r="Q321" s="5" t="s">
         <v>161</v>
@@ -12320,7 +12322,7 @@
       <c r="N322" s="391">
         <v>258050</v>
       </c>
-      <c r="O322" s="571"/>
+      <c r="O322" s="562"/>
       <c r="P322" s="558"/>
       <c r="Q322" s="142" t="s">
         <v>83</v>
@@ -12660,7 +12662,7 @@
       <c r="N336" s="420">
         <v>10000</v>
       </c>
-      <c r="O336" s="596">
+      <c r="O336" s="573">
         <f>+N336+N337+N338</f>
         <v>16000</v>
       </c>
@@ -12689,7 +12691,7 @@
       <c r="N337" s="424">
         <v>3000</v>
       </c>
-      <c r="O337" s="595"/>
+      <c r="O337" s="571"/>
       <c r="P337" s="202"/>
       <c r="Q337" s="5" t="s">
         <v>169</v>
@@ -12715,7 +12717,7 @@
       <c r="N338" s="424">
         <v>3000</v>
       </c>
-      <c r="O338" s="595"/>
+      <c r="O338" s="571"/>
       <c r="P338" s="202"/>
       <c r="Q338" s="5" t="s">
         <v>170</v>
@@ -12839,7 +12841,7 @@
       <c r="N343" s="41">
         <v>3000</v>
       </c>
-      <c r="O343" s="597">
+      <c r="O343" s="574">
         <f>+N343+N344</f>
         <v>8000</v>
       </c>
@@ -12868,7 +12870,7 @@
       <c r="N344" s="41">
         <v>5000</v>
       </c>
-      <c r="O344" s="597"/>
+      <c r="O344" s="574"/>
       <c r="P344" s="202"/>
       <c r="Q344" s="5" t="s">
         <v>175</v>
@@ -13417,7 +13419,7 @@
       <c r="N371" s="114">
         <v>2000</v>
       </c>
-      <c r="O371" s="598">
+      <c r="O371" s="575">
         <f>+N371+N372+N373</f>
         <v>18500</v>
       </c>
@@ -13446,7 +13448,7 @@
       <c r="N372" s="114">
         <v>8000</v>
       </c>
-      <c r="O372" s="598"/>
+      <c r="O372" s="575"/>
       <c r="P372" s="202"/>
       <c r="Q372" s="5" t="s">
         <v>190</v>
@@ -13472,7 +13474,7 @@
       <c r="N373" s="41">
         <v>8500</v>
       </c>
-      <c r="O373" s="598"/>
+      <c r="O373" s="575"/>
       <c r="P373" s="202"/>
       <c r="Q373" s="5" t="s">
         <v>191</v>
@@ -13628,7 +13630,7 @@
       <c r="N379" s="443">
         <v>10000</v>
       </c>
-      <c r="O379" s="599">
+      <c r="O379" s="576">
         <f>+N379+N380+N381+N382+N383</f>
         <v>31112.5</v>
       </c>
@@ -13657,7 +13659,7 @@
       <c r="N380" s="454">
         <v>7037.5</v>
       </c>
-      <c r="O380" s="600"/>
+      <c r="O380" s="577"/>
       <c r="P380" s="455"/>
       <c r="Q380" s="456" t="s">
         <v>199</v>
@@ -13684,7 +13686,7 @@
       <c r="N381" s="454">
         <v>7037.5</v>
       </c>
-      <c r="O381" s="600"/>
+      <c r="O381" s="577"/>
       <c r="P381" s="455"/>
       <c r="Q381" s="456" t="s">
         <v>200</v>
@@ -13711,7 +13713,7 @@
       <c r="N382" s="454">
         <v>1037.5</v>
       </c>
-      <c r="O382" s="600"/>
+      <c r="O382" s="577"/>
       <c r="P382" s="455"/>
       <c r="Q382" s="456" t="s">
         <v>201</v>
@@ -13738,7 +13740,7 @@
       <c r="N383" s="454">
         <v>6000</v>
       </c>
-      <c r="O383" s="600"/>
+      <c r="O383" s="577"/>
       <c r="P383" s="455"/>
       <c r="Q383" s="456" t="s">
         <v>201</v>
@@ -13896,7 +13898,7 @@
       <c r="N389" s="114">
         <v>3000</v>
       </c>
-      <c r="O389" s="575">
+      <c r="O389" s="578">
         <f>+N389+N390</f>
         <v>10000</v>
       </c>
@@ -13925,7 +13927,7 @@
       <c r="N390" s="114">
         <v>7000</v>
       </c>
-      <c r="O390" s="575"/>
+      <c r="O390" s="578"/>
       <c r="P390" s="202"/>
       <c r="Q390" s="5" t="s">
         <v>208</v>
@@ -13999,7 +14001,7 @@
       <c r="N393" s="114">
         <v>10000</v>
       </c>
-      <c r="O393" s="595">
+      <c r="O393" s="571">
         <f>+N393+N394+N395+N396+N397+N398+N399</f>
         <v>32800</v>
       </c>
@@ -14034,7 +14036,7 @@
       <c r="N394" s="114">
         <v>3800</v>
       </c>
-      <c r="O394" s="595"/>
+      <c r="O394" s="571"/>
       <c r="P394" s="475"/>
       <c r="Q394" s="5" t="s">
         <v>212</v>
@@ -14061,7 +14063,7 @@
       <c r="N395" s="114">
         <v>3800</v>
       </c>
-      <c r="O395" s="595"/>
+      <c r="O395" s="571"/>
       <c r="P395" s="475"/>
       <c r="Q395" s="5" t="s">
         <v>213</v>
@@ -14088,7 +14090,7 @@
       <c r="N396" s="114">
         <v>3800</v>
       </c>
-      <c r="O396" s="595"/>
+      <c r="O396" s="571"/>
       <c r="P396" s="475"/>
       <c r="Q396" s="5" t="s">
         <v>214</v>
@@ -14115,7 +14117,7 @@
       <c r="N397" s="41">
         <v>3800</v>
       </c>
-      <c r="O397" s="595"/>
+      <c r="O397" s="571"/>
       <c r="P397" s="476"/>
       <c r="Q397" s="5" t="s">
         <v>215</v>
@@ -14142,7 +14144,7 @@
       <c r="N398" s="41">
         <v>3800</v>
       </c>
-      <c r="O398" s="595"/>
+      <c r="O398" s="571"/>
       <c r="P398" s="476"/>
       <c r="Q398" s="5" t="s">
         <v>216</v>
@@ -14169,7 +14171,7 @@
       <c r="N399" s="41">
         <v>3800</v>
       </c>
-      <c r="O399" s="595"/>
+      <c r="O399" s="571"/>
       <c r="P399" s="476"/>
       <c r="Q399" s="5" t="s">
         <v>217</v>
@@ -14289,7 +14291,7 @@
       <c r="N403" s="186">
         <v>4000</v>
       </c>
-      <c r="O403" s="588">
+      <c r="O403" s="572">
         <f>+N404+N403</f>
         <v>5000</v>
       </c>
@@ -14322,7 +14324,7 @@
       <c r="N404" s="41">
         <v>1000</v>
       </c>
-      <c r="O404" s="572"/>
+      <c r="O404" s="560"/>
       <c r="P404" s="202"/>
       <c r="Q404" s="5" t="s">
         <v>222</v>
@@ -14620,7 +14622,7 @@
       <c r="N418" s="501">
         <v>10000</v>
       </c>
-      <c r="O418" s="583">
+      <c r="O418" s="565">
         <f>SUM(N418:N420)</f>
         <v>57300</v>
       </c>
@@ -14642,7 +14644,7 @@
       <c r="N419" s="501">
         <v>25000</v>
       </c>
-      <c r="O419" s="584"/>
+      <c r="O419" s="566"/>
       <c r="P419" s="557"/>
     </row>
     <row r="420" spans="2:22" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -14661,7 +14663,7 @@
       <c r="N420" s="501">
         <v>22300</v>
       </c>
-      <c r="O420" s="584"/>
+      <c r="O420" s="566"/>
       <c r="P420" s="557"/>
     </row>
     <row r="421" spans="2:22" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -15620,21 +15622,19 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="O284:O285"/>
-    <mergeCell ref="O317:O322"/>
-    <mergeCell ref="O200:O202"/>
-    <mergeCell ref="O418:O420"/>
-    <mergeCell ref="L225:L226"/>
-    <mergeCell ref="O225:O235"/>
-    <mergeCell ref="O393:O399"/>
-    <mergeCell ref="O403:O404"/>
-    <mergeCell ref="O336:O338"/>
-    <mergeCell ref="O343:O344"/>
-    <mergeCell ref="O371:O373"/>
-    <mergeCell ref="O379:O383"/>
-    <mergeCell ref="O389:O390"/>
-    <mergeCell ref="O258:O272"/>
-    <mergeCell ref="O280:O282"/>
+    <mergeCell ref="O67:O69"/>
+    <mergeCell ref="O26:O28"/>
+    <mergeCell ref="O30:O32"/>
+    <mergeCell ref="O35:O39"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="D7:U7"/>
+    <mergeCell ref="O12:O17"/>
+    <mergeCell ref="O19:O24"/>
+    <mergeCell ref="O96:O101"/>
+    <mergeCell ref="O131:O133"/>
+    <mergeCell ref="O144:O145"/>
+    <mergeCell ref="O149:O154"/>
+    <mergeCell ref="O71:O75"/>
     <mergeCell ref="O42:O44"/>
     <mergeCell ref="O48:O60"/>
     <mergeCell ref="P253:P255"/>
@@ -15651,19 +15651,21 @@
     <mergeCell ref="O77:O83"/>
     <mergeCell ref="O109:O112"/>
     <mergeCell ref="O121:O124"/>
-    <mergeCell ref="O96:O101"/>
-    <mergeCell ref="O131:O133"/>
-    <mergeCell ref="O144:O145"/>
-    <mergeCell ref="O149:O154"/>
-    <mergeCell ref="O71:O75"/>
-    <mergeCell ref="O26:O28"/>
-    <mergeCell ref="O30:O32"/>
-    <mergeCell ref="O35:O39"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="D7:U7"/>
-    <mergeCell ref="O12:O17"/>
-    <mergeCell ref="O19:O24"/>
-    <mergeCell ref="O67:O69"/>
+    <mergeCell ref="O284:O285"/>
+    <mergeCell ref="O317:O322"/>
+    <mergeCell ref="O200:O202"/>
+    <mergeCell ref="O418:O420"/>
+    <mergeCell ref="L225:L226"/>
+    <mergeCell ref="O225:O235"/>
+    <mergeCell ref="O393:O399"/>
+    <mergeCell ref="O403:O404"/>
+    <mergeCell ref="O336:O338"/>
+    <mergeCell ref="O343:O344"/>
+    <mergeCell ref="O371:O373"/>
+    <mergeCell ref="O379:O383"/>
+    <mergeCell ref="O389:O390"/>
+    <mergeCell ref="O258:O272"/>
+    <mergeCell ref="O280:O282"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G393" r:id="rId1" display="https://grupomaxx.sperant.com/clients/cce2203b-e7a728-0e21" xr:uid="{C086E48E-BBB3-4E00-A0A0-50DACC86631A}"/>
